--- a/5_Judgemental_Forecasts_Derivations_Analysis/0_Main/AR2/0_EDA_Tables/Forecast_Series_h3.xlsx
+++ b/5_Judgemental_Forecasts_Derivations_Analysis/0_Main/AR2/0_EDA_Tables/Forecast_Series_h3.xlsx
@@ -459,22 +459,22 @@
         <v>0.3500000000000085</v>
       </c>
       <c r="D2">
-        <v>0.538185828245611</v>
+        <v>0.3873625286719147</v>
       </c>
       <c r="E2">
         <v>0.8744122965642023</v>
       </c>
       <c r="F2">
-        <v>1.062598124809805</v>
+        <v>0.9117748252361084</v>
       </c>
       <c r="G2">
-        <v>-0.1881858282456025</v>
+        <v>-0.03736252867190615</v>
       </c>
       <c r="H2">
-        <v>0.1881858282456024</v>
+        <v>0.03736252867190615</v>
       </c>
       <c r="I2">
-        <v>0.3645179104666307</v>
+        <v>0.06673646755165363</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
@@ -497,22 +497,22 @@
         <v>0.3250000000000028</v>
       </c>
       <c r="D3">
-        <v>0.5431444915120298</v>
+        <v>0.4778567225039601</v>
       </c>
       <c r="E3">
         <v>4.12576201096553</v>
       </c>
       <c r="F3">
-        <v>4.343906502477557</v>
+        <v>4.278618733469487</v>
       </c>
       <c r="G3">
-        <v>-0.218144491512027</v>
+        <v>-0.1528567225039573</v>
       </c>
       <c r="H3">
-        <v>0.2181444915120272</v>
+        <v>0.152856722503957</v>
       </c>
       <c r="I3">
-        <v>1.847611531140469</v>
+        <v>1.284666095269703</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
@@ -535,22 +535,22 @@
         <v>-0.3000000000000114</v>
       </c>
       <c r="D4">
-        <v>0.53003263749601</v>
+        <v>0.3335052003695131</v>
       </c>
       <c r="E4">
         <v>-1.028039084203484</v>
       </c>
       <c r="F4">
-        <v>-0.1980064467074627</v>
+        <v>-0.3945338838339597</v>
       </c>
       <c r="G4">
-        <v>-0.8300326374960214</v>
+        <v>-0.6335052003695245</v>
       </c>
       <c r="H4">
-        <v>-0.8300326374960214</v>
+        <v>-0.6335052003695245</v>
       </c>
       <c r="I4">
-        <v>-1.017657805712223</v>
+        <v>-0.9012073731568299</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -573,31 +573,31 @@
         <v>-0.3000000000000114</v>
       </c>
       <c r="D5">
-        <v>0.4437531579660887</v>
+        <v>-3.445810778186758</v>
       </c>
       <c r="E5">
         <v>-0.4613515565679706</v>
       </c>
       <c r="F5">
-        <v>0.2824016013981296</v>
+        <v>-3.607162334754717</v>
       </c>
       <c r="G5">
-        <v>-0.7437531579661001</v>
+        <v>3.145810778186747</v>
       </c>
       <c r="H5">
-        <v>-0.1789499551698409</v>
+        <v>3.145810778186747</v>
       </c>
       <c r="I5">
-        <v>-0.1330945942754612</v>
+        <v>12.79877485052541</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -611,22 +611,22 @@
         <v>0.2000000000000028</v>
       </c>
       <c r="D6">
-        <v>0.4875209584480724</v>
+        <v>0.2677024867117838</v>
       </c>
       <c r="E6">
         <v>-0.498016164584866</v>
       </c>
       <c r="F6">
-        <v>-0.2104952061367964</v>
+        <v>-0.430313677873085</v>
       </c>
       <c r="G6">
-        <v>-0.2875209584480696</v>
+        <v>-0.06770248671178103</v>
       </c>
       <c r="H6">
-        <v>-0.2875209584480696</v>
+        <v>-0.06770248671178103</v>
       </c>
       <c r="I6">
-        <v>-0.2037118683812479</v>
+        <v>-0.06285023882315921</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -649,31 +649,31 @@
         <v>0.2999999999999829</v>
       </c>
       <c r="D7">
-        <v>0.4812595642375425</v>
+        <v>0.2098029729206569</v>
       </c>
       <c r="E7">
         <v>-1.199182264219526</v>
       </c>
       <c r="F7">
-        <v>-1.017922699981966</v>
+        <v>-1.289379291298852</v>
       </c>
       <c r="G7">
-        <v>-0.1812595642375596</v>
+        <v>0.090197027079326</v>
       </c>
       <c r="H7">
-        <v>-0.1812595642375596</v>
+        <v>0.09019702707932598</v>
       </c>
       <c r="I7">
-        <v>-0.4018714796800926</v>
+        <v>0.2244608540116608</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -687,31 +687,31 @@
         <v>0.5</v>
       </c>
       <c r="D8">
-        <v>0.5022044841138246</v>
+        <v>0.3335781136017746</v>
       </c>
       <c r="E8">
         <v>-0.00301810865190888</v>
       </c>
       <c r="F8">
-        <v>-0.0008136245380843121</v>
+        <v>-0.1694399950501343</v>
       </c>
       <c r="G8">
-        <v>-0.002204484113824567</v>
+        <v>0.1664218863982254</v>
       </c>
       <c r="H8">
-        <v>-0.002204484113824567</v>
+        <v>0.1664218863982254</v>
       </c>
       <c r="I8">
-        <v>-8.446994945754323E-06</v>
+        <v>0.02870080294275481</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -725,22 +725,22 @@
         <v>0.6</v>
       </c>
       <c r="D9">
-        <v>0.5093148203331452</v>
+        <v>0.3711231944667716</v>
       </c>
       <c r="E9">
         <v>0.08984239774072844</v>
       </c>
       <c r="F9">
-        <v>-0.0008427819261263014</v>
+        <v>-0.1390344077924999</v>
       </c>
       <c r="G9">
-        <v>0.09068517966685474</v>
+        <v>0.2288768055332284</v>
       </c>
       <c r="H9">
-        <v>-0.08899961581460214</v>
+        <v>0.04919201005177148</v>
       </c>
       <c r="I9">
-        <v>-0.008070946150428242</v>
+        <v>0.01125891011840792</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -749,7 +749,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -763,22 +763,22 @@
         <v>0.3</v>
       </c>
       <c r="D10">
-        <v>0.4987110170874532</v>
+        <v>0.3165851888571213</v>
       </c>
       <c r="E10">
         <v>0.066018718502528</v>
       </c>
       <c r="F10">
-        <v>0.2647297355899812</v>
+        <v>0.08260390735964929</v>
       </c>
       <c r="G10">
-        <v>-0.1987110170874532</v>
+        <v>-0.01658518885712129</v>
       </c>
       <c r="H10">
-        <v>0.1987110170874532</v>
+        <v>0.01658518885712129</v>
       </c>
       <c r="I10">
-        <v>0.06572336171282533</v>
+        <v>0.00246493431836549</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
@@ -801,31 +801,31 @@
         <v>0.4</v>
       </c>
       <c r="D11">
-        <v>0.4947615278300555</v>
+        <v>0.28448687342501</v>
       </c>
       <c r="E11">
         <v>0.3367145827682783</v>
       </c>
       <c r="F11">
-        <v>0.4314761105983338</v>
+        <v>0.2212014561932883</v>
       </c>
       <c r="G11">
-        <v>-0.09476152783005548</v>
+        <v>0.11551312657499</v>
       </c>
       <c r="H11">
-        <v>0.09476152783005548</v>
+        <v>-0.11551312657499</v>
       </c>
       <c r="I11">
-        <v>0.07279492376824982</v>
+        <v>-0.06444662602678451</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -839,31 +839,31 @@
         <v>0.4</v>
       </c>
       <c r="D12">
-        <v>0.4933803428144731</v>
+        <v>0.2909361803960807</v>
       </c>
       <c r="E12">
         <v>0.07767929089444053</v>
       </c>
       <c r="F12">
-        <v>0.1710596337089136</v>
+        <v>-0.03138452870947878</v>
       </c>
       <c r="G12">
-        <v>-0.09338034281447311</v>
+        <v>0.1090638196039193</v>
       </c>
       <c r="H12">
-        <v>0.09338034281447311</v>
+        <v>-0.04629476218496176</v>
       </c>
       <c r="I12">
-        <v>0.02322732605076459</v>
+        <v>-0.005049083591547014</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -877,31 +877,31 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="D13">
-        <v>0.4817676057522754</v>
+        <v>0.2170388845683362</v>
       </c>
       <c r="E13">
         <v>-0.4179231863442348</v>
       </c>
       <c r="F13">
-        <v>-0.336155580591965</v>
+        <v>-0.6008843017759042</v>
       </c>
       <c r="G13">
-        <v>-0.08176760575226971</v>
+        <v>0.1829611154316695</v>
       </c>
       <c r="H13">
-        <v>-0.08176760575226971</v>
+        <v>0.1829611154316695</v>
       </c>
       <c r="I13">
-        <v>-0.06165921532099686</v>
+        <v>0.186402154436598</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
       </c>
       <c r="K13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -915,22 +915,22 @@
         <v>0.6</v>
       </c>
       <c r="D14">
-        <v>0.4859848212562928</v>
+        <v>0.2871123118665653</v>
       </c>
       <c r="E14">
         <v>0.5337623012869103</v>
       </c>
       <c r="F14">
-        <v>0.4197471225432031</v>
+        <v>0.2208746131534756</v>
       </c>
       <c r="G14">
-        <v>0.1140151787437072</v>
+        <v>0.3128876881334347</v>
       </c>
       <c r="H14">
-        <v>-0.1140151787437071</v>
+        <v>-0.3128876881334347</v>
       </c>
       <c r="I14">
-        <v>-0.1087145473917996</v>
+        <v>-0.2361165995394009</v>
       </c>
       <c r="J14" t="b">
         <v>1</v>
@@ -953,22 +953,22 @@
         <v>0.5200000000000102</v>
       </c>
       <c r="D15">
-        <v>0.4899669100330906</v>
+        <v>0.3448896093780345</v>
       </c>
       <c r="E15">
         <v>0.2476995305164363</v>
       </c>
       <c r="F15">
-        <v>0.2176664405495167</v>
+        <v>0.07258913989446059</v>
       </c>
       <c r="G15">
-        <v>0.03003308996691961</v>
+        <v>0.1751103906219758</v>
       </c>
       <c r="H15">
-        <v>-0.03003308996691961</v>
+        <v>-0.1751103906219758</v>
       </c>
       <c r="I15">
-        <v>-0.01397637807656668</v>
+        <v>-0.05608587418744541</v>
       </c>
       <c r="J15" t="b">
         <v>1</v>
@@ -991,31 +991,31 @@
         <v>0.4200000000000017</v>
       </c>
       <c r="D16">
-        <v>0.474331834720193</v>
+        <v>0.2499297136152437</v>
       </c>
       <c r="E16">
         <v>0.1040735922691067</v>
       </c>
       <c r="F16">
-        <v>0.158405426989298</v>
+        <v>-0.06599669411565129</v>
       </c>
       <c r="G16">
-        <v>-0.05433183472019132</v>
+        <v>0.170070286384758</v>
       </c>
       <c r="H16">
-        <v>0.05433183472019132</v>
+        <v>-0.03807689815345544</v>
       </c>
       <c r="I16">
-        <v>0.01426096669186556</v>
+        <v>-0.006475748973601431</v>
       </c>
       <c r="J16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1029,31 +1029,31 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="D17">
-        <v>0.4770674433138691</v>
+        <v>0.334875446513568</v>
       </c>
       <c r="E17">
         <v>-0.2653114026982006</v>
       </c>
       <c r="F17">
-        <v>-0.1882439593843372</v>
+        <v>-0.3304359561846383</v>
       </c>
       <c r="G17">
-        <v>-0.07706744331386339</v>
+        <v>0.0651245534864377</v>
       </c>
       <c r="H17">
-        <v>-0.07706744331386339</v>
+        <v>0.0651245534864377</v>
       </c>
       <c r="I17">
-        <v>-0.03495435215699477</v>
+        <v>0.03879778073796944</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
       </c>
       <c r="K17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1067,31 +1067,31 @@
         <v>0.4490000000000123</v>
       </c>
       <c r="D18">
-        <v>0.4784455493468266</v>
+        <v>0.3215145075713155</v>
       </c>
       <c r="E18">
         <v>0.2578650222990987</v>
       </c>
       <c r="F18">
-        <v>0.287310571645913</v>
+        <v>0.1303795298704019</v>
       </c>
       <c r="G18">
-        <v>-0.02944554934681431</v>
+        <v>0.1274854924286968</v>
       </c>
       <c r="H18">
-        <v>0.02944554934681431</v>
+        <v>-0.1274854924286968</v>
       </c>
       <c r="I18">
-        <v>0.01605299485418664</v>
+        <v>-0.04949554791608764</v>
       </c>
       <c r="J18" t="b">
         <v>1</v>
       </c>
       <c r="K18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1105,31 +1105,31 @@
         <v>0.4799999999999898</v>
       </c>
       <c r="D19">
-        <v>0.4803480790267389</v>
+        <v>0.3632155774163528</v>
       </c>
       <c r="E19">
         <v>-0.1258961837583767</v>
       </c>
       <c r="F19">
-        <v>-0.1255481047316276</v>
+        <v>-0.2426806063420137</v>
       </c>
       <c r="G19">
-        <v>-0.0003480790267490486</v>
+        <v>0.116784422583637</v>
       </c>
       <c r="H19">
-        <v>-0.0003480790267490486</v>
+        <v>0.116784422583637</v>
       </c>
       <c r="I19">
-        <v>-8.75224832192073E-05</v>
+        <v>0.04304402760960448</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
       </c>
       <c r="K19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1143,31 +1143,31 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="D20">
-        <v>0.478021053783571</v>
+        <v>0.3543116169853093</v>
       </c>
       <c r="E20">
         <v>-0.4241758241758119</v>
       </c>
       <c r="F20">
-        <v>-0.3461547703922466</v>
+        <v>-0.4698642071905083</v>
       </c>
       <c r="G20">
-        <v>-0.07802105378356533</v>
+        <v>0.04568838301469641</v>
       </c>
       <c r="H20">
-        <v>-0.07802105378356533</v>
+        <v>0.04568838301469641</v>
       </c>
       <c r="I20">
-        <v>-0.06010200474992035</v>
+        <v>0.04084724338353563</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
       </c>
       <c r="K20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1181,31 +1181,31 @@
         <v>0.4499999999999886</v>
       </c>
       <c r="D21">
-        <v>0.48130241619056</v>
+        <v>0.4008430601108652</v>
       </c>
       <c r="E21">
         <v>0.1527192445571372</v>
       </c>
       <c r="F21">
-        <v>0.1840216607477086</v>
+        <v>0.1035623046680138</v>
       </c>
       <c r="G21">
-        <v>-0.03130241619057145</v>
+        <v>0.0491569398891234</v>
       </c>
       <c r="H21">
-        <v>0.03130241619057145</v>
+        <v>-0.0491569398891234</v>
       </c>
       <c r="I21">
-        <v>0.01054080396624209</v>
+        <v>-0.01259801670995217</v>
       </c>
       <c r="J21" t="b">
         <v>1</v>
       </c>
       <c r="K21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1219,22 +1219,22 @@
         <v>0.4999999999999858</v>
       </c>
       <c r="D22">
-        <v>0.489710673413228</v>
+        <v>0.4160513114798439</v>
       </c>
       <c r="E22">
         <v>0.6988415319443135</v>
       </c>
       <c r="F22">
-        <v>0.6885522053575558</v>
+        <v>0.6148928434241717</v>
       </c>
       <c r="G22">
-        <v>0.0102893265867578</v>
+        <v>0.08394868852014187</v>
       </c>
       <c r="H22">
-        <v>-0.01028932658675774</v>
+        <v>-0.08394868852014181</v>
       </c>
       <c r="I22">
-        <v>-0.01427534726752128</v>
+        <v>-0.110286277876012</v>
       </c>
       <c r="J22" t="b">
         <v>1</v>
@@ -1257,22 +1257,22 @@
         <v>0.4999999999999858</v>
       </c>
       <c r="D23">
-        <v>0.4886237948061168</v>
+        <v>0.4123934400676019</v>
       </c>
       <c r="E23">
         <v>0.4826764833261045</v>
       </c>
       <c r="F23">
-        <v>0.4713002781322354</v>
+        <v>0.3950699233937206</v>
       </c>
       <c r="G23">
-        <v>0.011376205193869</v>
+        <v>0.08760655993238387</v>
       </c>
       <c r="H23">
-        <v>-0.01137620519386906</v>
+        <v>-0.08760655993238387</v>
       </c>
       <c r="I23">
-        <v>-0.01085263538853276</v>
+        <v>-0.07689634318573496</v>
       </c>
       <c r="J23" t="b">
         <v>1</v>
@@ -1295,25 +1295,25 @@
         <v>0.5490000000000066</v>
       </c>
       <c r="D24">
-        <v>0.4854892101296538</v>
+        <v>0.370600716261984</v>
       </c>
       <c r="E24">
         <v>0.1246473542911689</v>
       </c>
       <c r="F24">
-        <v>0.06113656442081611</v>
+        <v>-0.0537519294468537</v>
       </c>
       <c r="G24">
-        <v>0.0635107898703528</v>
+        <v>0.1783992837380226</v>
       </c>
       <c r="H24">
-        <v>-0.0635107898703528</v>
+        <v>-0.07089542484431521</v>
       </c>
       <c r="I24">
-        <v>-0.01179928342260759</v>
+        <v>-0.01264769301252865</v>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="b">
         <v>0</v>
@@ -1333,22 +1333,22 @@
         <v>0.4999999999999858</v>
       </c>
       <c r="D25">
-        <v>0.4881679823589136</v>
+        <v>0.3542366545008231</v>
       </c>
       <c r="E25">
         <v>0.5746895714685679</v>
       </c>
       <c r="F25">
-        <v>0.5628575538274957</v>
+        <v>0.4289262259694052</v>
       </c>
       <c r="G25">
-        <v>0.01183201764107217</v>
+        <v>0.1457633454991627</v>
       </c>
       <c r="H25">
-        <v>-0.01183201764107222</v>
+        <v>-0.1457633454991627</v>
       </c>
       <c r="I25">
-        <v>-0.01345947765405403</v>
+        <v>-0.146290396230369</v>
       </c>
       <c r="J25" t="b">
         <v>1</v>
@@ -1371,22 +1371,22 @@
         <v>0.3</v>
       </c>
       <c r="D26">
-        <v>0.4806806885037083</v>
+        <v>0.3048298394574579</v>
       </c>
       <c r="E26">
         <v>0.2158406583130695</v>
       </c>
       <c r="F26">
-        <v>0.3965213468167779</v>
+        <v>0.2206704977705274</v>
       </c>
       <c r="G26">
-        <v>-0.1806806885037083</v>
+        <v>-0.004829839457457907</v>
       </c>
       <c r="H26">
-        <v>0.1806806885037083</v>
+        <v>0.004829839457457907</v>
       </c>
       <c r="I26">
-        <v>0.1106419887003722</v>
+        <v>0.002108278805273124</v>
       </c>
       <c r="J26" t="b">
         <v>1</v>
@@ -1409,31 +1409,31 @@
         <v>0.3500000000000085</v>
       </c>
       <c r="D27">
-        <v>0.4788916801365443</v>
+        <v>0.2913556369398622</v>
       </c>
       <c r="E27">
         <v>0.3220044792833222</v>
       </c>
       <c r="F27">
-        <v>0.4508961594198579</v>
+        <v>0.2633601162231758</v>
       </c>
       <c r="G27">
-        <v>-0.1288916801365358</v>
+        <v>0.05864436306014631</v>
       </c>
       <c r="H27">
-        <v>0.1288916801365358</v>
+        <v>-0.05864436306014631</v>
       </c>
       <c r="I27">
-        <v>0.09962046190105449</v>
+        <v>-0.03432833386143877</v>
       </c>
       <c r="J27" t="b">
         <v>1</v>
       </c>
       <c r="K27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -1447,22 +1447,22 @@
         <v>0.3</v>
       </c>
       <c r="D28">
-        <v>0.4813551927986502</v>
+        <v>0.3209990828340856</v>
       </c>
       <c r="E28">
         <v>2.521807318894706</v>
       </c>
       <c r="F28">
-        <v>2.703162511693356</v>
+        <v>2.542806401728791</v>
       </c>
       <c r="G28">
-        <v>-0.1813551927986502</v>
+        <v>-0.02099908283408564</v>
       </c>
       <c r="H28">
-        <v>0.1813551927986503</v>
+        <v>0.02099908283408558</v>
       </c>
       <c r="I28">
-        <v>0.9475754109934291</v>
+        <v>0.1063522430420187</v>
       </c>
       <c r="J28" t="b">
         <v>1</v>
@@ -1485,31 +1485,31 @@
         <v>0.3490000000000038</v>
       </c>
       <c r="D29">
-        <v>0.4723147938391146</v>
+        <v>0.2826276782706303</v>
       </c>
       <c r="E29">
         <v>10.039957649752</v>
       </c>
       <c r="F29">
-        <v>10.16327244359111</v>
+        <v>9.973585328022629</v>
       </c>
       <c r="G29">
-        <v>-0.1233147938391108</v>
+        <v>0.06637232172937352</v>
       </c>
       <c r="H29">
-        <v>0.1233147938391106</v>
+        <v>-0.06637232172937324</v>
       </c>
       <c r="I29">
-        <v>2.491357153844717</v>
+        <v>-1.328345313465505</v>
       </c>
       <c r="J29" t="b">
         <v>1</v>
       </c>
       <c r="K29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -1523,31 +1523,31 @@
         <v>0.3300000000000125</v>
       </c>
       <c r="D30">
-        <v>0.4704271382942627</v>
+        <v>0.2786771680534658</v>
       </c>
       <c r="E30">
         <v>-8.150304150385457</v>
       </c>
       <c r="F30">
-        <v>-8.009877012091208</v>
+        <v>-8.201626982332003</v>
       </c>
       <c r="G30">
-        <v>-0.1404271382942502</v>
+        <v>0.05132283194654669</v>
       </c>
       <c r="H30">
-        <v>-0.1404271382942497</v>
+        <v>0.05132283194654619</v>
       </c>
       <c r="I30">
-        <v>-2.269327994963248</v>
+        <v>0.839227413525947</v>
       </c>
       <c r="J30" t="b">
         <v>0</v>
       </c>
       <c r="K30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -1561,25 +1561,25 @@
         <v>1.699999999999989</v>
       </c>
       <c r="D31">
-        <v>0.4687862072861041</v>
+        <v>0.2688011788446484</v>
       </c>
       <c r="E31">
         <v>1.359367396593669</v>
       </c>
       <c r="F31">
-        <v>0.1281536038797836</v>
+        <v>-0.07183142456167213</v>
       </c>
       <c r="G31">
-        <v>1.231213792713885</v>
+        <v>1.431198821155341</v>
       </c>
       <c r="H31">
-        <v>-1.231213792713885</v>
+        <v>-1.287535972031996</v>
       </c>
       <c r="I31">
-        <v>-1.831456372734472</v>
+        <v>-1.842719965367289</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="b">
         <v>0</v>
@@ -1599,22 +1599,22 @@
         <v>2.2</v>
       </c>
       <c r="D32">
-        <v>0.4273771196711261</v>
+        <v>0.06551354746759229</v>
       </c>
       <c r="E32">
         <v>4.006937868393072</v>
       </c>
       <c r="F32">
-        <v>2.234314988064198</v>
+        <v>1.872451415860664</v>
       </c>
       <c r="G32">
-        <v>1.772622880328874</v>
+        <v>2.134486452532408</v>
       </c>
       <c r="H32">
-        <v>-1.772622880328874</v>
+        <v>-2.134486452532408</v>
       </c>
       <c r="I32">
-        <v>-11.0633876152741</v>
+        <v>-12.54947677640381</v>
       </c>
       <c r="J32" t="b">
         <v>1</v>
@@ -1637,22 +1637,22 @@
         <v>0.8250000000000028</v>
       </c>
       <c r="D33">
-        <v>0.0896746956836374</v>
+        <v>-3.626159446597504</v>
       </c>
       <c r="E33">
         <v>-0.8080921181302552</v>
       </c>
       <c r="F33">
-        <v>-1.543417422446621</v>
+        <v>-5.259251564727762</v>
       </c>
       <c r="G33">
-        <v>0.7353253043163654</v>
+        <v>4.451159446597507</v>
       </c>
       <c r="H33">
-        <v>0.7353253043163654</v>
+        <v>4.451159446597507</v>
       </c>
       <c r="I33">
-        <v>1.729124468527528</v>
+        <v>27.00671414970718</v>
       </c>
       <c r="J33" t="b">
         <v>0</v>
@@ -1675,31 +1675,31 @@
         <v>0.7060416926399853</v>
       </c>
       <c r="D34">
-        <v>0.5369886319520764</v>
+        <v>1.078814278518536</v>
       </c>
       <c r="E34">
         <v>-0.9882246039044738</v>
       </c>
       <c r="F34">
-        <v>-1.157277664592383</v>
+        <v>-0.6154520180259231</v>
       </c>
       <c r="G34">
-        <v>0.1690530606879089</v>
+        <v>-0.3727725858785507</v>
       </c>
       <c r="H34">
-        <v>0.1690530606879088</v>
+        <v>-0.3727725858785507</v>
       </c>
       <c r="I34">
-        <v>0.3627037252022451</v>
+        <v>-0.5978066812699728</v>
       </c>
       <c r="J34" t="b">
         <v>0</v>
       </c>
       <c r="K34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -1713,22 +1713,22 @@
         <v>0.8564599999999984</v>
       </c>
       <c r="D35">
-        <v>0.4522884875061418</v>
+        <v>0.1768169414264609</v>
       </c>
       <c r="E35">
         <v>1.203649640611794</v>
       </c>
       <c r="F35">
-        <v>0.7994781281179373</v>
+        <v>0.5240065820382563</v>
       </c>
       <c r="G35">
-        <v>0.4041715124938566</v>
+        <v>0.6796430585735376</v>
       </c>
       <c r="H35">
-        <v>-0.4041715124938565</v>
+        <v>-0.6796430585735375</v>
       </c>
       <c r="I35">
-        <v>-0.8096071800059395</v>
+        <v>-1.174189559325485</v>
       </c>
       <c r="J35" t="b">
         <v>1</v>
@@ -1751,22 +1751,22 @@
         <v>0.4867323308394456</v>
       </c>
       <c r="D36">
-        <v>0.4444250621926834</v>
+        <v>0.3077369798811567</v>
       </c>
       <c r="E36">
         <v>0.2513274344176</v>
       </c>
       <c r="F36">
-        <v>0.2090201657708378</v>
+        <v>0.07233208345931114</v>
       </c>
       <c r="G36">
-        <v>0.04230726864676221</v>
+        <v>0.1789953509582889</v>
       </c>
       <c r="H36">
-        <v>-0.04230726864676221</v>
+        <v>-0.1789953509582889</v>
       </c>
       <c r="I36">
-        <v>-0.01947604959206452</v>
+        <v>-0.05793354899336828</v>
       </c>
       <c r="J36" t="b">
         <v>1</v>
@@ -1789,22 +1789,22 @@
         <v>1.17</v>
       </c>
       <c r="D37">
-        <v>0.4566314938279677</v>
+        <v>0.4044511695641399</v>
       </c>
       <c r="E37">
         <v>1.030270144387512</v>
       </c>
       <c r="F37">
-        <v>0.3169016382154799</v>
+        <v>0.2647213139516521</v>
       </c>
       <c r="G37">
-        <v>0.7133685061720323</v>
+        <v>0.76554883043586</v>
       </c>
       <c r="H37">
-        <v>-0.7133685061720323</v>
+        <v>-0.7655488304358601</v>
       </c>
       <c r="I37">
-        <v>-0.9610299221126104</v>
+        <v>-0.9913791963559762</v>
       </c>
       <c r="J37" t="b">
         <v>1</v>
@@ -1827,25 +1827,25 @@
         <v>1.75</v>
       </c>
       <c r="D38">
-        <v>0.4598735387777314</v>
+        <v>0.2611022192826244</v>
       </c>
       <c r="E38">
         <v>1.349851107388789</v>
       </c>
       <c r="F38">
-        <v>0.05972464616652079</v>
+        <v>-0.1390466733285862</v>
       </c>
       <c r="G38">
-        <v>1.290126461222269</v>
+        <v>1.488897780717376</v>
       </c>
       <c r="H38">
-        <v>-1.290126461222268</v>
+        <v>-1.210804434060203</v>
       </c>
       <c r="I38">
-        <v>-1.818530978759025</v>
+        <v>-1.802764034754994</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="b">
         <v>0</v>
@@ -1865,22 +1865,22 @@
         <v>1.109885837708147</v>
       </c>
       <c r="D39">
-        <v>0.4583431352113039</v>
+        <v>0.3562814115568507</v>
       </c>
       <c r="E39">
         <v>1.545191941255428</v>
       </c>
       <c r="F39">
-        <v>0.8936492387585845</v>
+        <v>0.7915875151041314</v>
       </c>
       <c r="G39">
-        <v>0.6515427024968432</v>
+        <v>0.7536044261512964</v>
       </c>
       <c r="H39">
-        <v>-0.6515427024968433</v>
+        <v>-0.7536044261512964</v>
       </c>
       <c r="I39">
-        <v>-1.58900917338692</v>
+        <v>-1.761007341251984</v>
       </c>
       <c r="J39" t="b">
         <v>1</v>
@@ -1903,22 +1903,22 @@
         <v>1.04</v>
       </c>
       <c r="D40">
-        <v>0.4601389379573582</v>
+        <v>0.4301418904270196</v>
       </c>
       <c r="E40">
         <v>1.375226743644659</v>
       </c>
       <c r="F40">
-        <v>0.7953656816020174</v>
+        <v>0.7653686340716788</v>
       </c>
       <c r="G40">
-        <v>0.5798610620426419</v>
+        <v>0.6098581095729805</v>
       </c>
       <c r="H40">
-        <v>-0.5798610620426419</v>
+        <v>-0.6098581095729805</v>
       </c>
       <c r="I40">
-        <v>-1.258642028965252</v>
+        <v>-1.305459450414746</v>
       </c>
       <c r="J40" t="b">
         <v>1</v>
@@ -1941,22 +1941,22 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>0.4608215928450556</v>
+        <v>0.3584096246900327</v>
       </c>
       <c r="E41">
         <v>-0.01855976243503714</v>
       </c>
       <c r="F41">
-        <v>0.4422618304100184</v>
+        <v>0.3398498622549955</v>
       </c>
       <c r="G41">
-        <v>-0.4608215928450556</v>
+        <v>-0.3584096246900327</v>
       </c>
       <c r="H41">
-        <v>0.4237020679749813</v>
+        <v>0.3212900998199584</v>
       </c>
       <c r="I41">
-        <v>0.1952510618559749</v>
+        <v>0.1151534640930944</v>
       </c>
       <c r="J41" t="b">
         <v>1</v>
@@ -1979,22 +1979,22 @@
         <v>0.551740489547953</v>
       </c>
       <c r="D42">
-        <v>0.4607609824102413</v>
+        <v>0.3666656204007895</v>
       </c>
       <c r="E42">
         <v>0.6813581175453611</v>
       </c>
       <c r="F42">
-        <v>0.5903786104076495</v>
+        <v>0.4962832483981977</v>
       </c>
       <c r="G42">
-        <v>0.09097950713771163</v>
+        <v>0.1850748691471635</v>
       </c>
       <c r="H42">
-        <v>-0.09097950713771163</v>
+        <v>-0.1850748691471634</v>
       </c>
       <c r="I42">
-        <v>-0.115701980718091</v>
+        <v>-0.2179518217042909</v>
       </c>
       <c r="J42" t="b">
         <v>1</v>
@@ -2017,22 +2017,22 @@
         <v>0.56137382150105</v>
       </c>
       <c r="D43">
-        <v>0.4575276451677168</v>
+        <v>0.3721440140502105</v>
       </c>
       <c r="E43">
         <v>0.8484374385026132</v>
       </c>
       <c r="F43">
-        <v>0.7445912621692801</v>
+        <v>0.6592076310517737</v>
       </c>
       <c r="G43">
-        <v>0.1038461763333332</v>
+        <v>0.1892298074508394</v>
       </c>
       <c r="H43">
-        <v>-0.1038461763333332</v>
+        <v>-0.1892298074508395</v>
       </c>
       <c r="I43">
-        <v>-0.1654299393540341</v>
+        <v>-0.2852913862159842</v>
       </c>
       <c r="J43" t="b">
         <v>1</v>
@@ -2055,22 +2055,22 @@
         <v>0.5</v>
       </c>
       <c r="D44">
-        <v>0.4540797555180716</v>
+        <v>0.3982732797061906</v>
       </c>
       <c r="E44">
         <v>0.2864041604754924</v>
       </c>
       <c r="F44">
-        <v>0.240483915993564</v>
+        <v>0.184677440181683</v>
       </c>
       <c r="G44">
-        <v>0.04592024448192839</v>
+        <v>0.1017267202938094</v>
       </c>
       <c r="H44">
-        <v>-0.04592024448192839</v>
+        <v>-0.1017267202938094</v>
       </c>
       <c r="I44">
-        <v>-0.02419482928607205</v>
+        <v>-0.0479215862256125</v>
       </c>
       <c r="J44" t="b">
         <v>1</v>
@@ -2093,22 +2093,22 @@
         <v>0.5611476945050384</v>
       </c>
       <c r="D45">
-        <v>0.45383200752519</v>
+        <v>0.3277938830192304</v>
       </c>
       <c r="E45">
         <v>0.6279097355159999</v>
       </c>
       <c r="F45">
-        <v>0.5205940485361515</v>
+        <v>0.394555924030192</v>
       </c>
       <c r="G45">
-        <v>0.1073156869798484</v>
+        <v>0.233353811485808</v>
       </c>
       <c r="H45">
-        <v>-0.1073156869798484</v>
+        <v>-0.233353811485808</v>
       </c>
       <c r="I45">
-        <v>-0.1232524725845121</v>
+        <v>-0.2385962587684544</v>
       </c>
       <c r="J45" t="b">
         <v>1</v>
@@ -2131,31 +2131,31 @@
         <v>0.4391745998095615</v>
       </c>
       <c r="D46">
-        <v>0.4519560680546554</v>
+        <v>0.3035680348802827</v>
       </c>
       <c r="E46">
         <v>0.3339617829755114</v>
       </c>
       <c r="F46">
-        <v>0.3467432512206053</v>
+        <v>0.1983552180462326</v>
       </c>
       <c r="G46">
-        <v>-0.01278146824509391</v>
+        <v>0.1356065649292788</v>
       </c>
       <c r="H46">
-        <v>0.01278146824509391</v>
+        <v>-0.1356065649292788</v>
       </c>
       <c r="I46">
-        <v>0.008700409778853238</v>
+        <v>-0.07218567996201407</v>
       </c>
       <c r="J46" t="b">
         <v>1</v>
       </c>
       <c r="K46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -2169,22 +2169,22 @@
         <v>0.5319922642991344</v>
       </c>
       <c r="D47">
-        <v>0.4492096750021717</v>
+        <v>0.3180654933129406</v>
       </c>
       <c r="E47">
         <v>0.7326419872114158</v>
       </c>
       <c r="F47">
-        <v>0.6498593979144531</v>
+        <v>0.518715216225222</v>
       </c>
       <c r="G47">
-        <v>0.08278258929696269</v>
+        <v>0.2139267709861938</v>
       </c>
       <c r="H47">
-        <v>-0.08278258929696269</v>
+        <v>-0.2139267709861938</v>
       </c>
       <c r="I47">
-        <v>-0.1144470443673568</v>
+        <v>-0.2676988058815136</v>
       </c>
       <c r="J47" t="b">
         <v>1</v>
@@ -2207,31 +2207,31 @@
         <v>0.46</v>
       </c>
       <c r="D48">
-        <v>0.4482019312717844</v>
+        <v>0.322965769162406</v>
       </c>
       <c r="E48">
         <v>0.04831977022499523</v>
       </c>
       <c r="F48">
-        <v>0.03652170149677963</v>
+        <v>-0.0887144606125988</v>
       </c>
       <c r="G48">
-        <v>0.01179806872821559</v>
+        <v>0.137034230837594</v>
       </c>
       <c r="H48">
-        <v>-0.01179806872821559</v>
+        <v>0.04039469038760357</v>
       </c>
       <c r="I48">
-        <v>-0.00100096551437646</v>
+        <v>0.005535455327188009</v>
       </c>
       <c r="J48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" t="b">
         <v>0</v>
       </c>
       <c r="L48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -2245,31 +2245,31 @@
         <v>0.42</v>
       </c>
       <c r="D49">
-        <v>0.4499359708880525</v>
+        <v>0.2715408197250452</v>
       </c>
       <c r="E49">
         <v>0.6966911554241066</v>
       </c>
       <c r="F49">
-        <v>0.7266271263121592</v>
+        <v>0.5482319751491519</v>
       </c>
       <c r="G49">
-        <v>-0.0299359708880525</v>
+        <v>0.1484591802749548</v>
       </c>
       <c r="H49">
-        <v>0.02993597088805255</v>
+        <v>-0.1484591802749547</v>
       </c>
       <c r="I49">
-        <v>0.04260841464648985</v>
+        <v>-0.1848202674702364</v>
       </c>
       <c r="J49" t="b">
         <v>1</v>
       </c>
       <c r="K49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:12">
@@ -2283,22 +2283,22 @@
         <v>0.1088966743764388</v>
       </c>
       <c r="D50">
-        <v>0.447626467426591</v>
+        <v>0.2867219094086165</v>
       </c>
       <c r="E50">
         <v>0.1088966743764388</v>
       </c>
       <c r="F50">
-        <v>0.447626467426591</v>
+        <v>0.2867219094086165</v>
       </c>
       <c r="G50">
-        <v>-0.3387297930501522</v>
+        <v>-0.1778252350321777</v>
       </c>
       <c r="H50">
-        <v>0.3387297930501522</v>
+        <v>0.1778252350321777</v>
       </c>
       <c r="I50">
-        <v>0.1885109686505608</v>
+        <v>0.07035096764467476</v>
       </c>
       <c r="J50" t="b">
         <v>1</v>
